--- a/ci-cd-merge-resolver/repoCollector/datasets/hadoop.xlsx
+++ b/ci-cd-merge-resolver/repoCollector/datasets/hadoop.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>mergeCommit</t>
   </si>
@@ -42,6 +42,33 @@
   </si>
   <si>
     <t>isMultiModule</t>
+  </si>
+  <si>
+    <t>c10452516804eed793e575dedcd1ee7758ec1f4c</t>
+  </si>
+  <si>
+    <t>52d1d9603ecc03dbe3ef5fafa60377ef461ecca3</t>
+  </si>
+  <si>
+    <t>d3fa83a44b01c85f39bfb4deaf2972912ac61ca3</t>
+  </si>
+  <si>
+    <t>418cff4820ba73cdbfd09fc5879b8b3aa4e62d5f</t>
+  </si>
+  <si>
+    <t>7e228e54c56598e263d66e3ef74476e12a3b1f30</t>
+  </si>
+  <si>
+    <t>9119b3cf8f883aa2d5df534afc0c50249fed03c6</t>
+  </si>
+  <si>
+    <t>c275a9a6a07b2bd889bdba4d05b420027f430b34</t>
+  </si>
+  <si>
+    <t>44e19fc7f70b5c19f2b626fe247aea5d51ada51c</t>
+  </si>
+  <si>
+    <t>83cd84b70bac7b613eb4b2901d5ffe40098692eb</t>
   </si>
   <si>
     <t>9da62f33beb1373e468055e8df92f493bee97a82</t>
@@ -95,7 +122,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -141,13 +168,13 @@
         <v>12</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>102.0</v>
+        <v>6.0</v>
       </c>
       <c r="E2" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="F2" t="n" s="0">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G2" t="b" s="0">
         <v>0</v>
@@ -156,10 +183,106 @@
         <v>1</v>
       </c>
       <c r="I2" t="n" s="0">
-        <v>144.55499267578125</v>
+        <v>6.548999786376953</v>
       </c>
       <c r="J2" t="b" s="0">
-        <v>1</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="D3" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="E3" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F3" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G3" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H3" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n" s="0">
+        <v>6.425000190734863</v>
+      </c>
+      <c r="J3" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="D4" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="E4" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="F4" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="G4" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H4" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n" s="0">
+        <v>6.430999755859375</v>
+      </c>
+      <c r="J4" t="b" s="0">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="D5" t="n" s="0">
+        <v>144.0</v>
+      </c>
+      <c r="E5" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F5" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="G5" t="b" s="0">
+        <v>0</v>
+      </c>
+      <c r="H5" t="b" s="0">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n" s="0">
+        <v>395.2550048828125</v>
+      </c>
+      <c r="J5" t="b" s="0">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
